--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXV/LTAIPT_A63F35B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXV/LTAIPT_A63F35B.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="45">
   <si>
     <t>48997</t>
   </si>
@@ -127,31 +127,28 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>B54A6DE0AE8730A56C2E803649671B80</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>85D74E1467CA9596487837474C09C5E5</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Subdirección Jurídica.</t>
-  </si>
-  <si>
-    <t>12/01/2023</t>
-  </si>
-  <si>
-    <t>10/01/2023</t>
-  </si>
-  <si>
-    <t>Del periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no generó hipervínculo por alguna recomendación por  casos especiales.</t>
+    <t>Subdirección Jurídica</t>
+  </si>
+  <si>
+    <t>24/04/2023</t>
+  </si>
+  <si>
+    <t>Del periodo 01 de enero del 2023 al 31 de marzo del 2023 el Colegio de Bachilleres del Estado de Tlaxcala no generó hipervínculo por alguna recomendación por casos especiales</t>
   </si>
 </sst>
 </file>
@@ -547,7 +544,7 @@
   <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.5703125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.42578125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -559,7 +556,7 @@
     <col min="10" max="10" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="159.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="150.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
@@ -765,10 +762,10 @@
         <v>43</v>
       </c>
       <c r="L8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M8" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
